--- a/hira_material_automation/output/monthly/202601_202610__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__arthroscopy_suture_needle_detachable__040028__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:44</t>
+          <t>2026-10-14T23:47:17</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>87c5930eaf8a7bcf350122df8aae8d02eb7ed69b91b94ed2fde936d7926831ee</t>
+          <t>0289c9ea1dce11238d76018d98919ede3c49906ba26ead8ec794210179132287</t>
         </is>
       </c>
     </row>
